--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.789006140340092</v>
+        <v>9.833210225273264</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.6933018909832</v>
+        <v>10.84064884076044</v>
       </c>
     </row>
     <row r="9">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.52348208927351</v>
+        <v>13.70982713559656</v>
       </c>
       <c r="F11" t="n">
-        <v>10.6933018909832</v>
+        <v>10.84064884076044</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.6933018909832</v>
+        <v>10.84064884076044</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1036,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.985438456110451</v>
+        <v>3.881838524998495</v>
       </c>
       <c r="C2" t="n">
-        <v>6.887222298225268</v>
+        <v>6.70287287853535</v>
       </c>
       <c r="D2" t="n">
-        <v>9.789006140340092</v>
+        <v>9.523907232072213</v>
       </c>
       <c r="E2" t="n">
-        <v>12.69078998245492</v>
+        <v>12.34494158560907</v>
       </c>
       <c r="F2" t="n">
-        <v>15.59257382456973</v>
+        <v>15.16597593914593</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.985438456110451</v>
+        <v>4.036490021599021</v>
       </c>
       <c r="C3" t="n">
-        <v>6.887222298225268</v>
+        <v>6.857524375135876</v>
       </c>
       <c r="D3" t="n">
-        <v>9.789006140340092</v>
+        <v>9.678558728672739</v>
       </c>
       <c r="E3" t="n">
-        <v>12.69078998245492</v>
+        <v>12.4995930822096</v>
       </c>
       <c r="F3" t="n">
-        <v>15.59257382456973</v>
+        <v>15.32062743574645</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.985438456110451</v>
+        <v>4.191141518199547</v>
       </c>
       <c r="C4" t="n">
-        <v>6.887222298225268</v>
+        <v>7.012175871736401</v>
       </c>
       <c r="D4" t="n">
-        <v>9.789006140340092</v>
+        <v>9.833210225273264</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69078998245492</v>
+        <v>12.65424457881013</v>
       </c>
       <c r="F4" t="n">
-        <v>15.59257382456973</v>
+        <v>15.47527893234698</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.985438456110451</v>
+        <v>4.345793014800073</v>
       </c>
       <c r="C5" t="n">
-        <v>6.887222298225268</v>
+        <v>7.166827368336929</v>
       </c>
       <c r="D5" t="n">
-        <v>9.789006140340092</v>
+        <v>9.987861721873792</v>
       </c>
       <c r="E5" t="n">
-        <v>12.69078998245492</v>
+        <v>12.80889607541065</v>
       </c>
       <c r="F5" t="n">
-        <v>15.59257382456973</v>
+        <v>15.6299304289475</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.985438456110451</v>
+        <v>4.500444511400598</v>
       </c>
       <c r="C6" t="n">
-        <v>6.887222298225268</v>
+        <v>7.321478864937454</v>
       </c>
       <c r="D6" t="n">
-        <v>9.789006140340092</v>
+        <v>10.14251321847432</v>
       </c>
       <c r="E6" t="n">
-        <v>12.69078998245492</v>
+        <v>12.96354757201118</v>
       </c>
       <c r="F6" t="n">
-        <v>15.59257382456973</v>
+        <v>15.78458192554803</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>10.53</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>10.67</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>10.72</v>
+        <v>9.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.833210225273264</v>
+        <v>9.835783386850251</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.84064884076044</v>
+        <v>10.84922604601706</v>
       </c>
     </row>
     <row r="9">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.70982713559656</v>
+        <v>13.7206744569241</v>
       </c>
       <c r="F11" t="n">
-        <v>10.84064884076044</v>
+        <v>10.84922604601706</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.84064884076044</v>
+        <v>10.84922604601706</v>
       </c>
     </row>
     <row r="13">
@@ -1034,7 +1034,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.881838524998495</v>
+        <v>3.883897054260083</v>
       </c>
       <c r="C2" t="n">
-        <v>6.70287287853535</v>
+        <v>6.705188723954639</v>
       </c>
       <c r="D2" t="n">
-        <v>9.523907232072213</v>
+        <v>9.526480393649198</v>
       </c>
       <c r="E2" t="n">
-        <v>12.34494158560907</v>
+        <v>12.34777206334376</v>
       </c>
       <c r="F2" t="n">
-        <v>15.16597593914593</v>
+        <v>15.16906373303831</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.036490021599021</v>
+        <v>4.038548550860608</v>
       </c>
       <c r="C3" t="n">
-        <v>6.857524375135876</v>
+        <v>6.859840220555165</v>
       </c>
       <c r="D3" t="n">
-        <v>9.678558728672739</v>
+        <v>9.681131890249725</v>
       </c>
       <c r="E3" t="n">
-        <v>12.4995930822096</v>
+        <v>12.50242355994429</v>
       </c>
       <c r="F3" t="n">
-        <v>15.32062743574645</v>
+        <v>15.32371522963884</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.191141518199547</v>
+        <v>4.193200047461135</v>
       </c>
       <c r="C4" t="n">
-        <v>7.012175871736401</v>
+        <v>7.014491717155691</v>
       </c>
       <c r="D4" t="n">
-        <v>9.833210225273264</v>
+        <v>9.835783386850251</v>
       </c>
       <c r="E4" t="n">
-        <v>12.65424457881013</v>
+        <v>12.65707505654481</v>
       </c>
       <c r="F4" t="n">
-        <v>15.47527893234698</v>
+        <v>15.47836672623936</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.345793014800073</v>
+        <v>4.34785154406166</v>
       </c>
       <c r="C5" t="n">
-        <v>7.166827368336929</v>
+        <v>7.169143213756216</v>
       </c>
       <c r="D5" t="n">
-        <v>9.987861721873792</v>
+        <v>9.990434883450776</v>
       </c>
       <c r="E5" t="n">
-        <v>12.80889607541065</v>
+        <v>12.81172655314534</v>
       </c>
       <c r="F5" t="n">
-        <v>15.6299304289475</v>
+        <v>15.63301822283989</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.500444511400598</v>
+        <v>4.502503040662186</v>
       </c>
       <c r="C6" t="n">
-        <v>7.321478864937454</v>
+        <v>7.323794710356743</v>
       </c>
       <c r="D6" t="n">
-        <v>10.14251321847432</v>
+        <v>10.1450863800513</v>
       </c>
       <c r="E6" t="n">
-        <v>12.96354757201118</v>
+        <v>12.96637804974586</v>
       </c>
       <c r="F6" t="n">
-        <v>15.78458192554803</v>
+        <v>15.78766971944041</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.91</v>
+        <v>9.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.835783386850251</v>
+        <v>5.16189387351851</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.401450818635904</v>
+        <v>4.341423810040769</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.84922604601706</v>
+        <v>7.07632402163324</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.056836007731421e-24</v>
+        <v>181776.1226481434</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>1.172749178375119</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1851.949805673562</v>
+        <v>1538.734133841524</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>581.9498056735625</v>
+        <v>268.7341338415237</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.401450818635904</v>
+        <v>4.341423810040769</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.401450818635904</v>
+        <v>4.341423810040769</v>
       </c>
     </row>
     <row r="13">
@@ -764,8 +764,8 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.7206744569241</v>
+        <v>8.949204103659152</v>
       </c>
       <c r="F11" t="n">
-        <v>10.84922604601706</v>
+        <v>7.07632402163324</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.84922604601706</v>
+        <v>7.07632402163324</v>
       </c>
     </row>
     <row r="13">
@@ -1034,10 +1034,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.883897054260083</v>
+        <v>0.1447854435946949</v>
       </c>
       <c r="C2" t="n">
-        <v>6.705188723954639</v>
+        <v>2.498688161956076</v>
       </c>
       <c r="D2" t="n">
-        <v>9.526480393649198</v>
+        <v>4.852590880317458</v>
       </c>
       <c r="E2" t="n">
-        <v>12.34777206334376</v>
+        <v>7.206493598678842</v>
       </c>
       <c r="F2" t="n">
-        <v>15.16906373303831</v>
+        <v>9.560396317040228</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.038548550860608</v>
+        <v>0.2994369401952209</v>
       </c>
       <c r="C3" t="n">
-        <v>6.859840220555165</v>
+        <v>2.653339658556601</v>
       </c>
       <c r="D3" t="n">
-        <v>9.681131890249725</v>
+        <v>5.007242376917985</v>
       </c>
       <c r="E3" t="n">
-        <v>12.50242355994429</v>
+        <v>7.361145095279367</v>
       </c>
       <c r="F3" t="n">
-        <v>15.32371522963884</v>
+        <v>9.715047813640753</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.193200047461135</v>
+        <v>0.4540884367957466</v>
       </c>
       <c r="C4" t="n">
-        <v>7.014491717155691</v>
+        <v>2.807991155157127</v>
       </c>
       <c r="D4" t="n">
-        <v>9.835783386850251</v>
+        <v>5.16189387351851</v>
       </c>
       <c r="E4" t="n">
-        <v>12.65707505654481</v>
+        <v>7.515796591879894</v>
       </c>
       <c r="F4" t="n">
-        <v>15.47836672623936</v>
+        <v>9.869699310241279</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.34785154406166</v>
+        <v>0.6087399333962724</v>
       </c>
       <c r="C5" t="n">
-        <v>7.169143213756216</v>
+        <v>2.962642651757653</v>
       </c>
       <c r="D5" t="n">
-        <v>9.990434883450776</v>
+        <v>5.316545370119035</v>
       </c>
       <c r="E5" t="n">
-        <v>12.81172655314534</v>
+        <v>7.67044808848042</v>
       </c>
       <c r="F5" t="n">
-        <v>15.63301822283989</v>
+        <v>10.02435080684181</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.502503040662186</v>
+        <v>0.7633914299967985</v>
       </c>
       <c r="C6" t="n">
-        <v>7.323794710356743</v>
+        <v>3.117294148358179</v>
       </c>
       <c r="D6" t="n">
-        <v>10.1450863800513</v>
+        <v>5.471196866719563</v>
       </c>
       <c r="E6" t="n">
-        <v>12.96637804974586</v>
+        <v>7.825099585080945</v>
       </c>
       <c r="F6" t="n">
-        <v>15.78766971944041</v>
+        <v>10.17900230344233</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.9</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.91</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.92</v>
+        <v>5.24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.34</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.16189387351851</v>
+        <v>9.835783386850251</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.341423810040769</v>
+        <v>9.401450818635904</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.07632402163324</v>
+        <v>10.84922604601706</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>181776.1226481434</v>
+        <v>3.056836007731421e-24</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.172749178375119</v>
+        <v>1.97215226305253e-29</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1538.734133841524</v>
+        <v>1851.949805673562</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>268.7341338415237</v>
+        <v>581.9498056735625</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.341423810040769</v>
+        <v>9.401450818635904</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.341423810040769</v>
+        <v>9.401450818635904</v>
       </c>
     </row>
     <row r="13">
@@ -764,8 +764,8 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.949204103659152</v>
+        <v>13.7206744569241</v>
       </c>
       <c r="F11" t="n">
-        <v>7.07632402163324</v>
+        <v>10.84922604601706</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>7.07632402163324</v>
+        <v>10.84922604601706</v>
       </c>
     </row>
     <row r="13">
@@ -1034,10 +1034,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1447854435946949</v>
+        <v>3.883897054260083</v>
       </c>
       <c r="C2" t="n">
-        <v>2.498688161956076</v>
+        <v>6.705188723954639</v>
       </c>
       <c r="D2" t="n">
-        <v>4.852590880317458</v>
+        <v>9.526480393649198</v>
       </c>
       <c r="E2" t="n">
-        <v>7.206493598678842</v>
+        <v>12.34777206334376</v>
       </c>
       <c r="F2" t="n">
-        <v>9.560396317040228</v>
+        <v>15.16906373303831</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2994369401952209</v>
+        <v>4.038548550860608</v>
       </c>
       <c r="C3" t="n">
-        <v>2.653339658556601</v>
+        <v>6.859840220555165</v>
       </c>
       <c r="D3" t="n">
-        <v>5.007242376917985</v>
+        <v>9.681131890249725</v>
       </c>
       <c r="E3" t="n">
-        <v>7.361145095279367</v>
+        <v>12.50242355994429</v>
       </c>
       <c r="F3" t="n">
-        <v>9.715047813640753</v>
+        <v>15.32371522963884</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4540884367957466</v>
+        <v>4.193200047461135</v>
       </c>
       <c r="C4" t="n">
-        <v>2.807991155157127</v>
+        <v>7.014491717155691</v>
       </c>
       <c r="D4" t="n">
-        <v>5.16189387351851</v>
+        <v>9.835783386850251</v>
       </c>
       <c r="E4" t="n">
-        <v>7.515796591879894</v>
+        <v>12.65707505654481</v>
       </c>
       <c r="F4" t="n">
-        <v>9.869699310241279</v>
+        <v>15.47836672623936</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6087399333962724</v>
+        <v>4.34785154406166</v>
       </c>
       <c r="C5" t="n">
-        <v>2.962642651757653</v>
+        <v>7.169143213756216</v>
       </c>
       <c r="D5" t="n">
-        <v>5.316545370119035</v>
+        <v>9.990434883450776</v>
       </c>
       <c r="E5" t="n">
-        <v>7.67044808848042</v>
+        <v>12.81172655314534</v>
       </c>
       <c r="F5" t="n">
-        <v>10.02435080684181</v>
+        <v>15.63301822283989</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7633914299967985</v>
+        <v>4.502503040662186</v>
       </c>
       <c r="C6" t="n">
-        <v>3.117294148358179</v>
+        <v>7.323794710356743</v>
       </c>
       <c r="D6" t="n">
-        <v>5.471196866719563</v>
+        <v>10.1450863800513</v>
       </c>
       <c r="E6" t="n">
-        <v>7.825099585080945</v>
+        <v>12.96637804974586</v>
       </c>
       <c r="F6" t="n">
-        <v>10.17900230344233</v>
+        <v>15.78766971944041</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.23</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>5.24</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>5.24</v>
+        <v>9.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.835783386850251</v>
+        <v>9.270493610698153</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.401450818635904</v>
+        <v>8.798712858123366</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.84922604601706</v>
+        <v>10.37131536670599</v>
       </c>
     </row>
     <row r="9">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1370</v>
+        <v>-1373.1</v>
       </c>
     </row>
     <row r="8">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>581.9498056735625</v>
+        <v>544.8498056735625</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61900000</v>
+        <v>61923808</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.401450818635904</v>
+        <v>8.798712858123366</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.401450818635904</v>
+        <v>8.798712858123366</v>
       </c>
     </row>
     <row r="13">
@@ -765,7 +765,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,7 +813,7 @@
         <v>147500</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1407138529886914</v>
+        <v>0.1406597523847371</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>183500</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1927219305331179</v>
+        <v>0.1926478342546376</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>165500</v>
       </c>
       <c r="D4" t="n">
-        <v>0.394017366720517</v>
+        <v>0.3938658778865796</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>123500</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2726651857835218</v>
+        <v>0.2725603535234784</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -901,7 +901,7 @@
         <v>111500</v>
       </c>
       <c r="D6" t="n">
-        <v>0.38728049273021</v>
+        <v>0.3871315940389196</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -923,7 +923,7 @@
         <v>135500</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6752560581583199</v>
+        <v>0.6749964407873624</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>147500</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7446001615508885</v>
+        <v>0.7443138832805631</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>105500</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7831344911147011</v>
+        <v>0.7828333974551436</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.7206744569241</v>
+        <v>13.11627587378997</v>
       </c>
       <c r="F11" t="n">
-        <v>10.84922604601706</v>
+        <v>10.37131536670599</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.84922604601706</v>
+        <v>10.37131536670599</v>
       </c>
     </row>
     <row r="13">
@@ -1034,9 +1034,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.883897054260083</v>
+        <v>3.3208956146038</v>
       </c>
       <c r="C2" t="n">
-        <v>6.705188723954639</v>
+        <v>6.141102575294799</v>
       </c>
       <c r="D2" t="n">
-        <v>9.526480393649198</v>
+        <v>8.961309535985805</v>
       </c>
       <c r="E2" t="n">
-        <v>12.34777206334376</v>
+        <v>11.78151649667681</v>
       </c>
       <c r="F2" t="n">
-        <v>15.16906373303831</v>
+        <v>14.6017234573678</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.038548550860608</v>
+        <v>3.475487651959973</v>
       </c>
       <c r="C3" t="n">
-        <v>6.859840220555165</v>
+        <v>6.295694612650973</v>
       </c>
       <c r="D3" t="n">
-        <v>9.681131890249725</v>
+        <v>9.115901573341979</v>
       </c>
       <c r="E3" t="n">
-        <v>12.50242355994429</v>
+        <v>11.93610853403298</v>
       </c>
       <c r="F3" t="n">
-        <v>15.32371522963884</v>
+        <v>14.75631549472397</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.193200047461135</v>
+        <v>3.630079689316148</v>
       </c>
       <c r="C4" t="n">
-        <v>7.014491717155691</v>
+        <v>6.450286650007147</v>
       </c>
       <c r="D4" t="n">
-        <v>9.835783386850251</v>
+        <v>9.270493610698153</v>
       </c>
       <c r="E4" t="n">
-        <v>12.65707505654481</v>
+        <v>12.09070057138916</v>
       </c>
       <c r="F4" t="n">
-        <v>15.47836672623936</v>
+        <v>14.91090753208015</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.34785154406166</v>
+        <v>3.784671726672322</v>
       </c>
       <c r="C5" t="n">
-        <v>7.169143213756216</v>
+        <v>6.604878687363321</v>
       </c>
       <c r="D5" t="n">
-        <v>9.990434883450776</v>
+        <v>9.425085648054328</v>
       </c>
       <c r="E5" t="n">
-        <v>12.81172655314534</v>
+        <v>12.24529260874533</v>
       </c>
       <c r="F5" t="n">
-        <v>15.63301822283989</v>
+        <v>15.06549956943632</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.502503040662186</v>
+        <v>3.939263764028496</v>
       </c>
       <c r="C6" t="n">
-        <v>7.323794710356743</v>
+        <v>6.759470724719495</v>
       </c>
       <c r="D6" t="n">
-        <v>10.1450863800513</v>
+        <v>9.579677685410502</v>
       </c>
       <c r="E6" t="n">
-        <v>12.96637804974586</v>
+        <v>12.3998846461015</v>
       </c>
       <c r="F6" t="n">
-        <v>15.78766971944041</v>
+        <v>15.2200916067925</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.9</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.91</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.92</v>
+        <v>9.35</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.056836007731421e-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.21</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -1264,7 +1264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.29</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.32</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.66</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.54</v>
+        <v>5.5727</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5727</v>
+        <v>5.5025</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.270493610698153</v>
+        <v>9.271983520314647</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.37131536670599</v>
+        <v>10.3762817320943</v>
       </c>
     </row>
     <row r="9">
@@ -765,7 +765,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.11627587378997</v>
+        <v>13.12255667966849</v>
       </c>
       <c r="F11" t="n">
-        <v>10.37131536670599</v>
+        <v>10.3762817320943</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.37131536670599</v>
+        <v>10.3762817320943</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.3208956146038</v>
+        <v>3.322087542296996</v>
       </c>
       <c r="C2" t="n">
-        <v>6.141102575294799</v>
+        <v>6.142443493949644</v>
       </c>
       <c r="D2" t="n">
-        <v>8.961309535985805</v>
+        <v>8.962799445602299</v>
       </c>
       <c r="E2" t="n">
-        <v>11.78151649667681</v>
+        <v>11.78315539725495</v>
       </c>
       <c r="F2" t="n">
-        <v>14.6017234573678</v>
+        <v>14.6035113489076</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.475487651959973</v>
+        <v>3.47667957965317</v>
       </c>
       <c r="C3" t="n">
-        <v>6.295694612650973</v>
+        <v>6.297035531305817</v>
       </c>
       <c r="D3" t="n">
-        <v>9.115901573341979</v>
+        <v>9.117391482958473</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93610853403298</v>
+        <v>11.93774743461113</v>
       </c>
       <c r="F3" t="n">
-        <v>14.75631549472397</v>
+        <v>14.75810338626377</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.630079689316148</v>
+        <v>3.631271617009344</v>
       </c>
       <c r="C4" t="n">
-        <v>6.450286650007147</v>
+        <v>6.451627568661991</v>
       </c>
       <c r="D4" t="n">
-        <v>9.270493610698153</v>
+        <v>9.271983520314647</v>
       </c>
       <c r="E4" t="n">
-        <v>12.09070057138916</v>
+        <v>12.0923394719673</v>
       </c>
       <c r="F4" t="n">
-        <v>14.91090753208015</v>
+        <v>14.91269542361994</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.784671726672322</v>
+        <v>3.785863654365518</v>
       </c>
       <c r="C5" t="n">
-        <v>6.604878687363321</v>
+        <v>6.606219606018165</v>
       </c>
       <c r="D5" t="n">
-        <v>9.425085648054328</v>
+        <v>9.426575557670821</v>
       </c>
       <c r="E5" t="n">
-        <v>12.24529260874533</v>
+        <v>12.24693150932348</v>
       </c>
       <c r="F5" t="n">
-        <v>15.06549956943632</v>
+        <v>15.06728746097612</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.939263764028496</v>
+        <v>3.940455691721692</v>
       </c>
       <c r="C6" t="n">
-        <v>6.759470724719495</v>
+        <v>6.760811643374339</v>
       </c>
       <c r="D6" t="n">
-        <v>9.579677685410502</v>
+        <v>9.581167595026995</v>
       </c>
       <c r="E6" t="n">
-        <v>12.3998846461015</v>
+        <v>12.40152354667965</v>
       </c>
       <c r="F6" t="n">
-        <v>15.2200916067925</v>
+        <v>15.22187949833229</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.33</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5025</v>
+        <v>5.4152</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4152</v>
+        <v>5.7234</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7234</v>
+        <v>5.9711</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9711</v>
+        <v>6.407</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.271983520314647</v>
+        <v>9.311807160158075</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.3762817320943</v>
+        <v>10.50902719823906</v>
       </c>
     </row>
     <row r="9">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.12255667966849</v>
+        <v>13.29043568955173</v>
       </c>
       <c r="F11" t="n">
-        <v>10.3762817320943</v>
+        <v>10.50902719823906</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.3762817320943</v>
+        <v>10.50902719823906</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.322087542296996</v>
+        <v>3.353946454171738</v>
       </c>
       <c r="C2" t="n">
-        <v>6.142443493949644</v>
+        <v>6.178284769808728</v>
       </c>
       <c r="D2" t="n">
-        <v>8.962799445602299</v>
+        <v>9.002623085445727</v>
       </c>
       <c r="E2" t="n">
-        <v>11.78315539725495</v>
+        <v>11.82696140108272</v>
       </c>
       <c r="F2" t="n">
-        <v>14.6035113489076</v>
+        <v>14.65129971671971</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.47667957965317</v>
+        <v>3.508538491527912</v>
       </c>
       <c r="C3" t="n">
-        <v>6.297035531305817</v>
+        <v>6.332876807164903</v>
       </c>
       <c r="D3" t="n">
-        <v>9.117391482958473</v>
+        <v>9.157215122801901</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93774743461113</v>
+        <v>11.9815534384389</v>
       </c>
       <c r="F3" t="n">
-        <v>14.75810338626377</v>
+        <v>14.80589175407588</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.631271617009344</v>
+        <v>3.663130528884087</v>
       </c>
       <c r="C4" t="n">
-        <v>6.451627568661991</v>
+        <v>6.487468844521077</v>
       </c>
       <c r="D4" t="n">
-        <v>9.271983520314647</v>
+        <v>9.311807160158075</v>
       </c>
       <c r="E4" t="n">
-        <v>12.0923394719673</v>
+        <v>12.13614547579507</v>
       </c>
       <c r="F4" t="n">
-        <v>14.91269542361994</v>
+        <v>14.96048379143206</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.785863654365518</v>
+        <v>3.81772256624026</v>
       </c>
       <c r="C5" t="n">
-        <v>6.606219606018165</v>
+        <v>6.642060881877251</v>
       </c>
       <c r="D5" t="n">
-        <v>9.426575557670821</v>
+        <v>9.466399197514249</v>
       </c>
       <c r="E5" t="n">
-        <v>12.24693150932348</v>
+        <v>12.29073751315125</v>
       </c>
       <c r="F5" t="n">
-        <v>15.06728746097612</v>
+        <v>15.11507582878823</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.940455691721692</v>
+        <v>3.972314603596434</v>
       </c>
       <c r="C6" t="n">
-        <v>6.760811643374339</v>
+        <v>6.796652919233425</v>
       </c>
       <c r="D6" t="n">
-        <v>9.581167595026995</v>
+        <v>9.620991234870424</v>
       </c>
       <c r="E6" t="n">
-        <v>12.40152354667965</v>
+        <v>12.44532955050742</v>
       </c>
       <c r="F6" t="n">
-        <v>15.22187949833229</v>
+        <v>15.2696678661444</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.34</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.35</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.35</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.311807160158075</v>
+        <v>8.833600402532788</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.50902719823906</v>
+        <v>8.915004672821441</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111500</v>
+        <v>105700</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7875</v>
+        <v>2.6425</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147500</v>
+        <v>179650</v>
       </c>
       <c r="C2" t="n">
-        <v>147500</v>
+        <v>179650</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1406597523847371</v>
+        <v>0.1870879977213288</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>179650</v>
       </c>
       <c r="C3" t="n">
-        <v>183500</v>
+        <v>179650</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1926478342546376</v>
+        <v>0.1870879977213288</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165500</v>
+        <v>105700</v>
       </c>
       <c r="C4" t="n">
-        <v>165500</v>
+        <v>105700</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3938658778865796</v>
+        <v>0.2211499170076879</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123500</v>
+        <v>105700</v>
       </c>
       <c r="C5" t="n">
-        <v>123500</v>
+        <v>105700</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2725603535234784</v>
+        <v>0.2211499170076879</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111500</v>
+        <v>48850</v>
       </c>
       <c r="C6" t="n">
-        <v>111500</v>
+        <v>48850</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3871315940389196</v>
+        <v>0.1157104832764807</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135500</v>
+        <v>48850</v>
       </c>
       <c r="C7" t="n">
-        <v>135500</v>
+        <v>48850</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6749964407873624</v>
+        <v>0.1744667414510425</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147500</v>
+        <v>48850</v>
       </c>
       <c r="C8" t="n">
-        <v>147500</v>
+        <v>48850</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7443138832805631</v>
+        <v>0.1744667414510425</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105500</v>
+        <v>48850</v>
       </c>
       <c r="C9" t="n">
-        <v>105500</v>
+        <v>48850</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7828333974551436</v>
+        <v>0.2919792578001663</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.29043568955173</v>
+        <v>11.27452560937708</v>
       </c>
       <c r="F11" t="n">
-        <v>10.50902719823906</v>
+        <v>8.915004672821441</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10.50902719823906</v>
+        <v>8.915004672821441</v>
       </c>
     </row>
     <row r="13">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
   </sheetData>
@@ -1035,7 +1035,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.353946454171738</v>
+        <v>3.019201723834037</v>
       </c>
       <c r="C2" t="n">
-        <v>6.178284769808728</v>
+        <v>5.843540039471028</v>
       </c>
       <c r="D2" t="n">
-        <v>9.002623085445727</v>
+        <v>8.667878355108027</v>
       </c>
       <c r="E2" t="n">
-        <v>11.82696140108272</v>
+        <v>11.49221667074502</v>
       </c>
       <c r="F2" t="n">
-        <v>14.65129971671971</v>
+        <v>14.31655498638201</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.508538491527912</v>
+        <v>3.102062747546419</v>
       </c>
       <c r="C3" t="n">
-        <v>6.332876807164903</v>
+        <v>5.926401063183409</v>
       </c>
       <c r="D3" t="n">
-        <v>9.157215122801901</v>
+        <v>8.750739378820407</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9815534384389</v>
+        <v>11.5750776944574</v>
       </c>
       <c r="F3" t="n">
-        <v>14.80589175407588</v>
+        <v>14.39941601009439</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.663130528884087</v>
+        <v>3.184923771258799</v>
       </c>
       <c r="C4" t="n">
-        <v>6.487468844521077</v>
+        <v>6.00926208689579</v>
       </c>
       <c r="D4" t="n">
-        <v>9.311807160158075</v>
+        <v>8.833600402532788</v>
       </c>
       <c r="E4" t="n">
-        <v>12.13614547579507</v>
+        <v>11.65793871816978</v>
       </c>
       <c r="F4" t="n">
-        <v>14.96048379143206</v>
+        <v>14.48227703380677</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.81772256624026</v>
+        <v>3.267784794971181</v>
       </c>
       <c r="C5" t="n">
-        <v>6.642060881877251</v>
+        <v>6.092123110608171</v>
       </c>
       <c r="D5" t="n">
-        <v>9.466399197514249</v>
+        <v>8.916461426245169</v>
       </c>
       <c r="E5" t="n">
-        <v>12.29073751315125</v>
+        <v>11.74079974188217</v>
       </c>
       <c r="F5" t="n">
-        <v>15.11507582878823</v>
+        <v>14.56513805751915</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.972314603596434</v>
+        <v>3.350645818683561</v>
       </c>
       <c r="C6" t="n">
-        <v>6.796652919233425</v>
+        <v>6.174984134320552</v>
       </c>
       <c r="D6" t="n">
-        <v>9.620991234870424</v>
+        <v>8.99932244995755</v>
       </c>
       <c r="E6" t="n">
-        <v>12.44532955050742</v>
+        <v>11.82366076559455</v>
       </c>
       <c r="F6" t="n">
-        <v>15.2696678661444</v>
+        <v>14.64799908123153</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.380000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.390000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.390000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1264,7 +1264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.407</v>
+        <v>6.2576</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.833600402532788</v>
+        <v>9.634173059386065</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.798712858123366</v>
+        <v>9.621933839938288</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.915004672821441</v>
+        <v>9.662731238097543</v>
       </c>
     </row>
     <row r="9">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1851.949805673562</v>
+        <v>1856.660783693041</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>11.828</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-0.6860000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1373.1</v>
+        <v>-1271.976</v>
       </c>
     </row>
     <row r="8">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>544.8498056735625</v>
+        <v>595.8267836930413</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.798712858123366</v>
+        <v>9.621933839938288</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.798712858123366</v>
+        <v>9.621933839938288</v>
       </c>
     </row>
     <row r="13">
@@ -835,7 +835,7 @@
         <v>179650</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1870879977213288</v>
+        <v>0.4347342866898625</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11.27452560937708</v>
+        <v>12.22015184496591</v>
       </c>
       <c r="F11" t="n">
-        <v>8.915004672821441</v>
+        <v>9.662731238097543</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8.915004672821441</v>
+        <v>9.662731238097543</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.019201723834037</v>
+        <v>3.792993439345711</v>
       </c>
       <c r="C2" t="n">
-        <v>5.843540039471028</v>
+        <v>6.621490894587846</v>
       </c>
       <c r="D2" t="n">
-        <v>8.667878355108027</v>
+        <v>9.449988349829983</v>
       </c>
       <c r="E2" t="n">
-        <v>11.49221667074502</v>
+        <v>12.27848580507212</v>
       </c>
       <c r="F2" t="n">
-        <v>14.31655498638201</v>
+        <v>15.10698326031425</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.102062747546419</v>
+        <v>3.885085794123751</v>
       </c>
       <c r="C3" t="n">
-        <v>5.926401063183409</v>
+        <v>6.713583249365887</v>
       </c>
       <c r="D3" t="n">
-        <v>8.750739378820407</v>
+        <v>9.542080704608024</v>
       </c>
       <c r="E3" t="n">
-        <v>11.5750776944574</v>
+        <v>12.37057815985016</v>
       </c>
       <c r="F3" t="n">
-        <v>14.39941601009439</v>
+        <v>15.19907561509229</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.184923771258799</v>
+        <v>3.977178148901792</v>
       </c>
       <c r="C4" t="n">
-        <v>6.00926208689579</v>
+        <v>6.805675604143927</v>
       </c>
       <c r="D4" t="n">
-        <v>8.833600402532788</v>
+        <v>9.634173059386065</v>
       </c>
       <c r="E4" t="n">
-        <v>11.65793871816978</v>
+        <v>12.4626705146282</v>
       </c>
       <c r="F4" t="n">
-        <v>14.48227703380677</v>
+        <v>15.29116796987033</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.267784794971181</v>
+        <v>4.069270503679832</v>
       </c>
       <c r="C5" t="n">
-        <v>6.092123110608171</v>
+        <v>6.897767958921968</v>
       </c>
       <c r="D5" t="n">
-        <v>8.916461426245169</v>
+        <v>9.726265414164105</v>
       </c>
       <c r="E5" t="n">
-        <v>11.74079974188217</v>
+        <v>12.55476286940624</v>
       </c>
       <c r="F5" t="n">
-        <v>14.56513805751915</v>
+        <v>15.38326032464837</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.350645818683561</v>
+        <v>4.161362858457873</v>
       </c>
       <c r="C6" t="n">
-        <v>6.174984134320552</v>
+        <v>6.989860313700008</v>
       </c>
       <c r="D6" t="n">
-        <v>8.99932244995755</v>
+        <v>9.818357768942144</v>
       </c>
       <c r="E6" t="n">
-        <v>11.82366076559455</v>
+        <v>12.64685522418428</v>
       </c>
       <c r="F6" t="n">
-        <v>14.64799908123153</v>
+        <v>15.47535267942641</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>8.869999999999999</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>8.880000000000001</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>8.880000000000001</v>
+        <v>9.69</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2576</v>
+        <v>6.7429</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.7429</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.32</v>
+        <v>4.9444</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.634173059386065</v>
+        <v>4.698912168775854</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.13</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.621933839938288</v>
+        <v>4.920915193337636</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.662731238097543</v>
+        <v>4.180905111465027</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>203012.933396102</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.422904737312788</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1856.660783693041</v>
+        <v>691.6558076165227</v>
       </c>
     </row>
     <row r="3">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1271.976</v>
+        <v>-398.076</v>
       </c>
     </row>
     <row r="8">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>595.8267836930413</v>
+        <v>304.7218076165227</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.621933839938288</v>
+        <v>4.920915193337636</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.621933839938288</v>
+        <v>4.920915193337636</v>
       </c>
     </row>
     <row r="13">
@@ -967,7 +967,7 @@
         <v>48850</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2919792578001663</v>
+        <v>0.1744667414510425</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.22015184496591</v>
+        <v>5.287459006420208</v>
       </c>
       <c r="F11" t="n">
-        <v>9.662731238097543</v>
+        <v>4.180905111465027</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.662731238097543</v>
+        <v>4.180905111465027</v>
       </c>
     </row>
     <row r="13">
@@ -1035,10 +1035,10 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.792993439345711</v>
+        <v>2.494544026620189</v>
       </c>
       <c r="C2" t="n">
-        <v>6.621490894587846</v>
+        <v>3.509656066021094</v>
       </c>
       <c r="D2" t="n">
-        <v>9.449988349829983</v>
+        <v>4.524768105421998</v>
       </c>
       <c r="E2" t="n">
-        <v>12.27848580507212</v>
+        <v>5.539880144822905</v>
       </c>
       <c r="F2" t="n">
-        <v>15.10698326031425</v>
+        <v>6.554992184223808</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.885085794123751</v>
+        <v>2.581616058297117</v>
       </c>
       <c r="C3" t="n">
-        <v>6.713583249365887</v>
+        <v>3.596728097698021</v>
       </c>
       <c r="D3" t="n">
-        <v>9.542080704608024</v>
+        <v>4.611840137098926</v>
       </c>
       <c r="E3" t="n">
-        <v>12.37057815985016</v>
+        <v>5.626952176499833</v>
       </c>
       <c r="F3" t="n">
-        <v>15.19907561509229</v>
+        <v>6.642064215900735</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.977178148901792</v>
+        <v>2.668688089974045</v>
       </c>
       <c r="C4" t="n">
-        <v>6.805675604143927</v>
+        <v>3.683800129374949</v>
       </c>
       <c r="D4" t="n">
-        <v>9.634173059386065</v>
+        <v>4.698912168775854</v>
       </c>
       <c r="E4" t="n">
-        <v>12.4626705146282</v>
+        <v>5.71402420817676</v>
       </c>
       <c r="F4" t="n">
-        <v>15.29116796987033</v>
+        <v>6.729136247577664</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.069270503679832</v>
+        <v>2.755760121650972</v>
       </c>
       <c r="C5" t="n">
-        <v>6.897767958921968</v>
+        <v>3.770872161051877</v>
       </c>
       <c r="D5" t="n">
-        <v>9.726265414164105</v>
+        <v>4.785984200452781</v>
       </c>
       <c r="E5" t="n">
-        <v>12.55476286940624</v>
+        <v>5.801096239853688</v>
       </c>
       <c r="F5" t="n">
-        <v>15.38326032464837</v>
+        <v>6.816208279254591</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.161362858457873</v>
+        <v>2.8428321533279</v>
       </c>
       <c r="C6" t="n">
-        <v>6.989860313700008</v>
+        <v>3.857944192728804</v>
       </c>
       <c r="D6" t="n">
-        <v>9.818357768942144</v>
+        <v>4.873056232129709</v>
       </c>
       <c r="E6" t="n">
-        <v>12.64685522418428</v>
+        <v>5.888168271530615</v>
       </c>
       <c r="F6" t="n">
-        <v>15.47535267942641</v>
+        <v>6.903280310931518</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>9.68</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>9.69</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>9.69</v>
+        <v>4.76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/brut_fv_report.xlsx
+++ b/outputs/brut_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9444</v>
+        <v>4.9446</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>203012.933396102</v>
+        <v>203062.0909719341</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.422904737312788</v>
+        <v>1.423249279635074</v>
       </c>
     </row>
   </sheetData>
